--- a/data_lake/bart_temp_med/dt=2026-07-20/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-07-20/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858E2959-3323-459F-BEC2-9DA0C8B1B547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0203F39-F55F-41C0-ADDC-392A631C53FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AB$1:$AB$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AC$1:$AC$210</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6348,8 +6348,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="105" width="32.42578125" style="50" customWidth="1"/>
-    <col min="106" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="106" width="32.42578125" style="50" customWidth="1"/>
+    <col min="107" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6686,7 +6686,9 @@
       <c r="AB5" s="56">
         <v>29.2</v>
       </c>
-      <c r="AC5" s="56"/>
+      <c r="AC5" s="56">
+        <v>29.4</v>
+      </c>
       <c r="AD5" s="56"/>
       <c r="AE5" s="56"/>
       <c r="AF5" s="56"/>
@@ -6701,11 +6703,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.922222222222224</v>
+        <v>28.94736842105263</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6713,7 +6715,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.76900733325095416</v>
+        <v>0.79415353208135997</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6801,7 +6803,9 @@
       <c r="AB6" s="56">
         <v>28.9</v>
       </c>
-      <c r="AC6" s="56"/>
+      <c r="AC6" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AD6" s="56"/>
       <c r="AE6" s="56"/>
       <c r="AF6" s="56"/>
@@ -6816,11 +6820,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.93333333333333</v>
+        <v>28.899999999999995</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6828,7 +6832,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.53809944438451041</v>
+        <v>0.50476611105117541</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6916,7 +6920,9 @@
       <c r="AB7" s="56">
         <v>31.9</v>
       </c>
-      <c r="AC7" s="56"/>
+      <c r="AC7" s="56">
+        <v>31.6</v>
+      </c>
       <c r="AD7" s="56"/>
       <c r="AE7" s="56"/>
       <c r="AF7" s="56"/>
@@ -6931,11 +6937,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>32.044444444444444</v>
+        <v>32.021052631578947</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6943,7 +6949,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.8442639528929838</v>
+        <v>2.8208721400274861</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7031,7 +7037,9 @@
       <c r="AB8" s="56">
         <v>30.9</v>
       </c>
-      <c r="AC8" s="56"/>
+      <c r="AC8" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AD8" s="56"/>
       <c r="AE8" s="56"/>
       <c r="AF8" s="56"/>
@@ -7046,11 +7054,11 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>30.077777777777776</v>
+        <v>30.047368421052632</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7058,7 +7066,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4992384616063745</v>
+        <v>1.4688291048812303</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7146,7 +7154,9 @@
       <c r="AB9" s="56">
         <v>29.8</v>
       </c>
-      <c r="AC9" s="56"/>
+      <c r="AC9" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AD9" s="56"/>
       <c r="AE9" s="56"/>
       <c r="AF9" s="56"/>
@@ -7161,11 +7171,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.705555555555559</v>
+        <v>29.684210526315791</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7173,7 +7183,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-8.1913427074670864E-2</v>
+        <v>-0.10325845631443897</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7261,7 +7271,9 @@
       <c r="AB10" s="56">
         <v>31.8</v>
       </c>
-      <c r="AC10" s="56"/>
+      <c r="AC10" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AD10" s="56"/>
       <c r="AE10" s="56"/>
       <c r="AF10" s="56"/>
@@ -7276,11 +7288,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.877777777777776</v>
+        <v>31.810526315789474</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7288,7 +7300,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.7983557433727171</v>
+        <v>1.7311042813844146</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7376,7 +7388,9 @@
       <c r="AB11" s="56">
         <v>32.799999999999997</v>
       </c>
-      <c r="AC11" s="56"/>
+      <c r="AC11" s="56">
+        <v>32.5</v>
+      </c>
       <c r="AD11" s="56"/>
       <c r="AE11" s="56"/>
       <c r="AF11" s="56"/>
@@ -7391,11 +7405,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>33.138888888888886</v>
+        <v>33.105263157894733</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7403,7 +7417,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>3.134974811661035</v>
+        <v>3.101349080666882</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7491,7 +7505,9 @@
       <c r="AB12" s="56">
         <v>31.5</v>
       </c>
-      <c r="AC12" s="56"/>
+      <c r="AC12" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AD12" s="56"/>
       <c r="AE12" s="56"/>
       <c r="AF12" s="56"/>
@@ -7506,11 +7522,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.561111111111106</v>
+        <v>30.452631578947365</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7518,7 +7534,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>2.2954447217955263</v>
+        <v>2.1869651896317848</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7606,7 +7622,9 @@
       <c r="AB13" s="56">
         <v>30.8</v>
       </c>
-      <c r="AC13" s="56"/>
+      <c r="AC13" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AD13" s="56"/>
       <c r="AE13" s="56"/>
       <c r="AF13" s="56"/>
@@ -7621,11 +7639,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>30.449999999999996</v>
+        <v>30.352631578947364</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7633,7 +7651,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>2.1206053021876343</v>
+        <v>2.0232368811350021</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7721,7 +7739,9 @@
       <c r="AB14" s="56">
         <v>23.5</v>
       </c>
-      <c r="AC14" s="56"/>
+      <c r="AC14" s="56">
+        <v>22.9</v>
+      </c>
       <c r="AD14" s="56"/>
       <c r="AE14" s="56"/>
       <c r="AF14" s="56"/>
@@ -7736,11 +7756,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.95</v>
+        <v>23.89473684210526</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7748,7 +7768,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>2.2284599761051496</v>
+        <v>2.1731968182104104</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7836,7 +7856,9 @@
       <c r="AB15" s="56">
         <v>28</v>
       </c>
-      <c r="AC15" s="56"/>
+      <c r="AC15" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AD15" s="56"/>
       <c r="AE15" s="56"/>
       <c r="AF15" s="56"/>
@@ -7851,11 +7873,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.216666666666665</v>
+        <v>29.178947368421053</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7863,7 +7885,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.9811612903225857</v>
+        <v>0.94344199207697343</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7951,7 +7973,9 @@
       <c r="AB16" s="56">
         <v>27.8</v>
       </c>
-      <c r="AC16" s="56"/>
+      <c r="AC16" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AD16" s="56"/>
       <c r="AE16" s="56"/>
       <c r="AF16" s="56"/>
@@ -7966,11 +7990,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.644444444444446</v>
+        <v>28.55263157894737</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7978,7 +8002,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>1.0067915960414666</v>
+        <v>0.91497873054439083</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8066,7 +8090,9 @@
       <c r="AB17" s="56">
         <v>26.8</v>
       </c>
-      <c r="AC17" s="56"/>
+      <c r="AC17" s="56">
+        <v>24.4</v>
+      </c>
       <c r="AD17" s="56"/>
       <c r="AE17" s="56"/>
       <c r="AF17" s="56"/>
@@ -8081,11 +8107,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>25.011111111111116</v>
+        <v>24.978947368421057</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8093,7 +8119,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>1.0274874419549178</v>
+        <v>0.99532369926485842</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8181,7 +8207,9 @@
       <c r="AB18" s="56">
         <v>18.899999999999999</v>
       </c>
-      <c r="AC18" s="56"/>
+      <c r="AC18" s="56">
+        <v>19.399999999999999</v>
+      </c>
       <c r="AD18" s="56"/>
       <c r="AE18" s="56"/>
       <c r="AF18" s="56"/>
@@ -8196,11 +8224,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.822222222222223</v>
+        <v>18.852631578947367</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8208,7 +8236,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.4038709677419412</v>
+        <v>1.4342803244670854</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8296,7 +8324,9 @@
       <c r="AB19" s="56">
         <v>24.2</v>
       </c>
-      <c r="AC19" s="56"/>
+      <c r="AC19" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AD19" s="56"/>
       <c r="AE19" s="56"/>
       <c r="AF19" s="56"/>
@@ -8311,11 +8341,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.727777777777774</v>
+        <v>24.563157894736843</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8323,7 +8353,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.5942428315412229</v>
+        <v>2.4296229485002918</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8411,7 +8441,9 @@
       <c r="AB20" s="56">
         <v>22.8</v>
       </c>
-      <c r="AC20" s="56"/>
+      <c r="AC20" s="56">
+        <v>21.5</v>
+      </c>
       <c r="AD20" s="56"/>
       <c r="AE20" s="56"/>
       <c r="AF20" s="56"/>
@@ -8426,11 +8458,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.716666666666669</v>
+        <v>24.547368421052635</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8438,7 +8470,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>2.1090012406947984</v>
+        <v>1.9397029950807649</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8526,7 +8558,9 @@
       <c r="AB21" s="56">
         <v>26</v>
       </c>
-      <c r="AC21" s="56"/>
+      <c r="AC21" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AD21" s="56"/>
       <c r="AE21" s="56"/>
       <c r="AF21" s="56"/>
@@ -8541,11 +8575,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.194444444444443</v>
+        <v>27.178947368421053</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8553,7 +8587,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.5043625526873114</v>
+        <v>2.4888654766639213</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8641,7 +8675,9 @@
       <c r="AB22" s="56">
         <v>15.2</v>
       </c>
-      <c r="AC22" s="56"/>
+      <c r="AC22" s="56">
+        <v>15</v>
+      </c>
       <c r="AD22" s="56"/>
       <c r="AE22" s="56"/>
       <c r="AF22" s="56"/>
@@ -8656,11 +8692,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.56111111111111</v>
+        <v>15.53157894736842</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8668,7 +8704,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.7807781913427103</v>
+        <v>1.7512460276000201</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8756,7 +8792,9 @@
       <c r="AB23" s="56">
         <v>26</v>
       </c>
-      <c r="AC23" s="56"/>
+      <c r="AC23" s="56">
+        <v>24.2</v>
+      </c>
       <c r="AD23" s="56"/>
       <c r="AE23" s="56"/>
       <c r="AF23" s="56"/>
@@ -8771,11 +8809,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.311111111111106</v>
+        <v>26.199999999999996</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8871,7 +8909,9 @@
       <c r="AB24" s="56">
         <v>26.2</v>
       </c>
-      <c r="AC24" s="56"/>
+      <c r="AC24" s="56">
+        <v>28.2</v>
+      </c>
       <c r="AD24" s="56"/>
       <c r="AE24" s="56"/>
       <c r="AF24" s="56"/>
@@ -8886,11 +8926,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.255555555555556</v>
+        <v>29.200000000000003</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8898,7 +8938,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>0.89319707081943633</v>
+        <v>0.83764151526388275</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8986,7 +9026,9 @@
       <c r="AB25" s="56">
         <v>22.2</v>
       </c>
-      <c r="AC25" s="56"/>
+      <c r="AC25" s="56">
+        <v>18.899999999999999</v>
+      </c>
       <c r="AD25" s="56"/>
       <c r="AE25" s="56"/>
       <c r="AF25" s="56"/>
@@ -9001,11 +9043,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>22.37222222222222</v>
+        <v>22.189473684210522</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9013,7 +9055,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>2.43879776602002</v>
+        <v>2.2560492280083224</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9101,7 +9143,9 @@
       <c r="AB26" s="56">
         <v>11.6</v>
       </c>
-      <c r="AC26" s="56"/>
+      <c r="AC26" s="56">
+        <v>11.6</v>
+      </c>
       <c r="AD26" s="56"/>
       <c r="AE26" s="56"/>
       <c r="AF26" s="56"/>
@@ -9116,11 +9160,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.738888888888887</v>
+        <v>11.731578947368419</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9128,7 +9172,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.3685739887352977</v>
+        <v>1.3612640472148296</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9216,7 +9260,9 @@
       <c r="AB27" s="56">
         <v>28.5</v>
       </c>
-      <c r="AC27" s="56"/>
+      <c r="AC27" s="56">
+        <v>25.5</v>
+      </c>
       <c r="AD27" s="56"/>
       <c r="AE27" s="56"/>
       <c r="AF27" s="56"/>
@@ -9231,11 +9277,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.461111111111109</v>
+        <v>28.305263157894736</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9243,7 +9289,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.4724051415152601</v>
+        <v>1.3165571882988871</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9331,7 +9377,9 @@
       <c r="AB28" s="56">
         <v>28.7</v>
       </c>
-      <c r="AC28" s="56"/>
+      <c r="AC28" s="56">
+        <v>27.5</v>
+      </c>
       <c r="AD28" s="56"/>
       <c r="AE28" s="56"/>
       <c r="AF28" s="56"/>
@@ -9346,11 +9394,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.688888888888886</v>
+        <v>26.731578947368419</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9358,7 +9406,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.93747033741194485</v>
+        <v>0.98016039589147752</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9446,7 +9494,9 @@
       <c r="AB29" s="56">
         <v>25.8</v>
       </c>
-      <c r="AC29" s="56"/>
+      <c r="AC29" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AD29" s="56"/>
       <c r="AE29" s="56"/>
       <c r="AF29" s="56"/>
@@ -9461,11 +9511,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.694444444444443</v>
+        <v>27.610526315789475</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9473,7 +9523,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.74040223018720397</v>
+        <v>0.6564841015322358</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9561,7 +9611,9 @@
       <c r="AB30" s="56">
         <v>24.4</v>
       </c>
-      <c r="AC30" s="56"/>
+      <c r="AC30" s="56">
+        <v>24.9</v>
+      </c>
       <c r="AD30" s="56"/>
       <c r="AE30" s="56"/>
       <c r="AF30" s="56"/>
@@ -9576,11 +9628,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.116666666666667</v>
+        <v>25.105263157894736</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9588,7 +9640,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.59866518353729603</v>
+        <v>0.58726167476536517</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9676,7 +9728,9 @@
       <c r="AB31" s="98">
         <v>28</v>
       </c>
-      <c r="AC31" s="98"/>
+      <c r="AC31" s="98">
+        <v>27.7</v>
+      </c>
       <c r="AD31" s="98"/>
       <c r="AE31" s="98"/>
       <c r="AF31" s="98"/>
@@ -9691,11 +9745,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.611111111111107</v>
+        <v>26.668421052631576</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9703,7 +9757,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.2421624850657089</v>
+        <v>1.2994724265861777</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9791,7 +9845,9 @@
       <c r="AB32" s="56">
         <v>20.266666666666669</v>
       </c>
-      <c r="AC32" s="56"/>
+      <c r="AC32" s="56">
+        <v>20.966666666666669</v>
+      </c>
       <c r="AD32" s="56"/>
       <c r="AE32" s="56"/>
       <c r="AF32" s="56"/>
@@ -9806,11 +9862,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.55925925925926</v>
+        <v>20.580701754385963</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9818,7 +9874,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.9024032071504209</v>
+        <v>2.9238457022771236</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9906,7 +9962,9 @@
       <c r="AB33" s="56">
         <v>28.25</v>
       </c>
-      <c r="AC33" s="56"/>
+      <c r="AC33" s="56">
+        <v>27.25</v>
+      </c>
       <c r="AD33" s="56"/>
       <c r="AE33" s="56"/>
       <c r="AF33" s="56"/>
@@ -9921,11 +9979,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>28.113888888888887</v>
+        <v>28.068421052631578</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9933,7 +9991,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.2864168076763356</v>
+        <v>1.2409489714190265</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10021,7 +10079,9 @@
       <c r="AB34" s="56">
         <v>22</v>
       </c>
-      <c r="AC34" s="56"/>
+      <c r="AC34" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AD34" s="56"/>
       <c r="AE34" s="56"/>
       <c r="AF34" s="56"/>
@@ -10036,11 +10096,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.462962962962965</v>
+        <v>21.442105263157895</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10048,7 +10108,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.6757653712826439</v>
+        <v>1.6549076714775737</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10136,7 +10196,9 @@
       <c r="AB35" s="56">
         <v>25.8</v>
       </c>
-      <c r="AC35" s="56"/>
+      <c r="AC35" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AD35" s="56"/>
       <c r="AE35" s="56"/>
       <c r="AF35" s="56"/>
@@ -10151,11 +10213,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.669444444444448</v>
+        <v>24.747368421052634</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10163,7 +10225,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.63119654472704667</v>
+        <v>0.70912052133523318</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10251,7 +10313,9 @@
       <c r="AB36" s="56">
         <v>20.45</v>
       </c>
-      <c r="AC36" s="56"/>
+      <c r="AC36" s="56">
+        <v>19.850000000000001</v>
+      </c>
       <c r="AD36" s="56"/>
       <c r="AE36" s="56"/>
       <c r="AF36" s="56"/>
@@ -10266,11 +10330,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>20.302777777777781</v>
+        <v>20.278947368421058</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10278,7 +10342,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.3039667145593903</v>
+        <v>1.2801363052026673</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10366,7 +10430,9 @@
       <c r="AB37" s="56">
         <v>27.95</v>
       </c>
-      <c r="AC37" s="56"/>
+      <c r="AC37" s="56">
+        <v>26.85</v>
+      </c>
       <c r="AD37" s="56"/>
       <c r="AE37" s="56"/>
       <c r="AF37" s="56"/>
@@ -10381,11 +10447,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.494444444444447</v>
+        <v>27.460526315789473</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10393,7 +10459,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.6082145705070658</v>
+        <v>1.5742964418520913</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10479,7 +10545,9 @@
       <c r="AB38" s="56">
         <v>15.95</v>
       </c>
-      <c r="AC38" s="56"/>
+      <c r="AC38" s="56">
+        <v>15.5</v>
+      </c>
       <c r="AD38" s="56"/>
       <c r="AE38" s="56"/>
       <c r="AF38" s="56"/>
@@ -10494,11 +10562,11 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>16.123529411764704</v>
+        <v>16.088888888888889</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10506,7 +10574,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>1.1056004048140231</v>
+        <v>1.070959881938208</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10592,7 +10660,9 @@
       <c r="AB39" s="56">
         <v>23.2</v>
       </c>
-      <c r="AC39" s="56"/>
+      <c r="AC39" s="56">
+        <v>21.4</v>
+      </c>
       <c r="AD39" s="56"/>
       <c r="AE39" s="56"/>
       <c r="AF39" s="56"/>
@@ -10607,11 +10677,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.870588235294122</v>
+        <v>22.788888888888891</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10701,7 +10771,9 @@
       <c r="AB40" s="56">
         <v>26.2</v>
       </c>
-      <c r="AC40" s="56"/>
+      <c r="AC40" s="56">
+        <v>24.8</v>
+      </c>
       <c r="AD40" s="56"/>
       <c r="AE40" s="56"/>
       <c r="AF40" s="56"/>
@@ -10716,11 +10788,11 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.506666666666664</v>
+        <v>25.462499999999999</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10728,7 +10800,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.6548759182396928</v>
+        <v>2.6107092515730272</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10931,7 +11003,9 @@
       <c r="AB42" s="56">
         <v>28.6</v>
       </c>
-      <c r="AC42" s="56"/>
+      <c r="AC42" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AD42" s="56"/>
       <c r="AE42" s="56"/>
       <c r="AF42" s="56"/>
@@ -10946,11 +11020,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>28.238888888888891</v>
+        <v>28.252631578947366</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10958,7 +11032,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.48620337183061935</v>
+        <v>0.4999460618890943</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11042,7 +11116,9 @@
       <c r="AB43" s="56">
         <v>30.5</v>
       </c>
-      <c r="AC43" s="56"/>
+      <c r="AC43" s="56">
+        <v>29.4</v>
+      </c>
       <c r="AD43" s="56"/>
       <c r="AE43" s="56"/>
       <c r="AF43" s="56"/>
@@ -11057,11 +11133,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.737500000000001</v>
+        <v>29.71764705882353</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11157,7 +11233,9 @@
       <c r="AB44" s="56">
         <v>30.05</v>
       </c>
-      <c r="AC44" s="56"/>
+      <c r="AC44" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AD44" s="56"/>
       <c r="AE44" s="56"/>
       <c r="AF44" s="56"/>
@@ -11172,11 +11250,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.676388888888887</v>
+        <v>28.680263157894736</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11184,7 +11262,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.3340454446060654</v>
+        <v>1.3379197136119139</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11272,7 +11350,9 @@
       <c r="AB45" s="56">
         <v>29.65</v>
       </c>
-      <c r="AC45" s="56"/>
+      <c r="AC45" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AD45" s="56"/>
       <c r="AE45" s="56"/>
       <c r="AF45" s="56"/>
@@ -11287,11 +11367,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.184722222222224</v>
+        <v>29.148684210526319</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11299,7 +11379,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.2785245903247429</v>
+        <v>1.2424865786288386</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11658,7 +11738,9 @@
       <c r="AB49" s="56">
         <v>29.6</v>
       </c>
-      <c r="AC49" s="56"/>
+      <c r="AC49" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AD49" s="56"/>
       <c r="AE49" s="56"/>
       <c r="AF49" s="56"/>
@@ -11673,11 +11755,11 @@
       <c r="AO49" s="56"/>
       <c r="AP49" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ49" s="71">
         <f t="shared" si="1"/>
-        <v>29.777777777777779</v>
+        <v>29.726315789473681</v>
       </c>
       <c r="AR49" s="71">
         <f>IFERROR(VLOOKUP(A49,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11685,7 +11767,7 @@
       </c>
       <c r="AS49" s="71">
         <f t="shared" si="2"/>
-        <v>2.4890874317459577</v>
+        <v>2.4376254434418598</v>
       </c>
     </row>
     <row r="50" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11959,7 +12041,9 @@
       <c r="AB52" s="56">
         <v>29.7</v>
       </c>
-      <c r="AC52" s="56"/>
+      <c r="AC52" s="56">
+        <v>27.85</v>
+      </c>
       <c r="AD52" s="56"/>
       <c r="AE52" s="56"/>
       <c r="AF52" s="56"/>
@@ -11974,11 +12058,11 @@
       <c r="AO52" s="56"/>
       <c r="AP52" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ52" s="71">
         <f t="shared" si="1"/>
-        <v>29.488888888888887</v>
+        <v>29.402631578947368</v>
       </c>
       <c r="AR52" s="71">
         <f>IFERROR(VLOOKUP(A52,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11986,7 +12070,7 @@
       </c>
       <c r="AS52" s="71">
         <f t="shared" si="2"/>
-        <v>2.1296425922983389</v>
+        <v>2.0433852823568195</v>
       </c>
     </row>
     <row r="53" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12074,7 +12158,9 @@
       <c r="AB53" s="56">
         <v>31.3</v>
       </c>
-      <c r="AC53" s="56"/>
+      <c r="AC53" s="56">
+        <v>28.95</v>
+      </c>
       <c r="AD53" s="56"/>
       <c r="AE53" s="56"/>
       <c r="AF53" s="56"/>
@@ -12089,11 +12175,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>30.55833333333333</v>
+        <v>30.473684210526315</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12101,7 +12187,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>2.060107308266911</v>
+        <v>1.975458185459896</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12177,7 +12263,9 @@
       <c r="AB54" s="56">
         <v>29.95</v>
       </c>
-      <c r="AC54" s="56"/>
+      <c r="AC54" s="56">
+        <v>30.3</v>
+      </c>
       <c r="AD54" s="56"/>
       <c r="AE54" s="56"/>
       <c r="AF54" s="56"/>
@@ -12192,7 +12280,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12292,7 +12380,9 @@
       <c r="AB55" s="56">
         <v>30.45</v>
       </c>
-      <c r="AC55" s="56"/>
+      <c r="AC55" s="56">
+        <v>29.25</v>
+      </c>
       <c r="AD55" s="56"/>
       <c r="AE55" s="56"/>
       <c r="AF55" s="56"/>
@@ -12307,11 +12397,11 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>29.960526315789473</v>
       </c>
       <c r="AR55" s="71" t="str">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12565,7 +12655,9 @@
       <c r="AB58" s="56">
         <v>29.65</v>
       </c>
-      <c r="AC58" s="99"/>
+      <c r="AC58" s="99">
+        <v>29</v>
+      </c>
       <c r="AD58" s="56"/>
       <c r="AE58" s="56"/>
       <c r="AF58" s="56"/>
@@ -12580,11 +12672,11 @@
       <c r="AO58" s="56"/>
       <c r="AP58" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ58" s="71">
         <f t="shared" si="1"/>
-        <v>29.448611111111106</v>
+        <v>29.424999999999997</v>
       </c>
       <c r="AR58" s="71">
         <f>IFERROR(VLOOKUP(A58,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12592,7 +12684,7 @@
       </c>
       <c r="AS58" s="71">
         <f t="shared" si="2"/>
-        <v>1.3343912820289461</v>
+        <v>1.3107801709178375</v>
       </c>
     </row>
     <row r="59" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12674,7 +12766,9 @@
       <c r="AB59" s="56">
         <v>26.3</v>
       </c>
-      <c r="AC59" s="56"/>
+      <c r="AC59" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AD59" s="56"/>
       <c r="AE59" s="56"/>
       <c r="AF59" s="56"/>
@@ -12689,11 +12783,11 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>25.653333333333332</v>
+        <v>25.618750000000002</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12701,7 +12795,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>1.508769118385004</v>
+        <v>1.4741857850516737</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12789,7 +12883,9 @@
       <c r="AB60" s="56">
         <v>27.05</v>
       </c>
-      <c r="AC60" s="56"/>
+      <c r="AC60" s="56">
+        <v>25.45</v>
+      </c>
       <c r="AD60" s="56"/>
       <c r="AE60" s="56"/>
       <c r="AF60" s="56"/>
@@ -12804,11 +12900,11 @@
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ60" s="71">
         <f t="shared" si="1"/>
-        <v>26.62777777777778</v>
+        <v>26.565789473684212</v>
       </c>
       <c r="AR60" s="71">
         <f>IFERROR(VLOOKUP(A60,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12816,7 +12912,7 @@
       </c>
       <c r="AS60" s="71">
         <f t="shared" si="2"/>
-        <v>0.92110609605181892</v>
+        <v>0.85911779195825133</v>
       </c>
     </row>
     <row r="61" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12904,7 +13000,9 @@
       <c r="AB61" s="56">
         <v>25.4</v>
       </c>
-      <c r="AC61" s="56"/>
+      <c r="AC61" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="AD61" s="56"/>
       <c r="AE61" s="56"/>
       <c r="AF61" s="56"/>
@@ -12919,11 +13017,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>25.685185185185187</v>
+        <v>25.719298245614038</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12931,7 +13029,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>1.1461812452212961</v>
+        <v>1.1802943056501469</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13155,7 +13253,9 @@
       </c>
       <c r="AA64" s="56"/>
       <c r="AB64" s="56"/>
-      <c r="AC64" s="56"/>
+      <c r="AC64" s="56">
+        <v>24.8</v>
+      </c>
       <c r="AD64" s="56"/>
       <c r="AE64" s="56"/>
       <c r="AF64" s="56"/>
@@ -13170,7 +13270,7 @@
       <c r="AO64" s="56"/>
       <c r="AP64" s="58">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ64" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13270,7 +13370,9 @@
       <c r="AB65" s="56">
         <v>25.65</v>
       </c>
-      <c r="AC65" s="56"/>
+      <c r="AC65" s="56">
+        <v>24.7</v>
+      </c>
       <c r="AD65" s="56"/>
       <c r="AE65" s="56"/>
       <c r="AF65" s="56"/>
@@ -13285,11 +13387,11 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.730555555555558</v>
+        <v>25.676315789473687</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13297,7 +13399,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.82144072527656675</v>
+        <v>0.767200959194696</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13381,7 +13483,9 @@
       <c r="AB66" s="56">
         <v>24.45</v>
       </c>
-      <c r="AC66" s="56"/>
+      <c r="AC66" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AD66" s="56"/>
       <c r="AE66" s="56"/>
       <c r="AF66" s="56"/>
@@ -13396,11 +13500,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.309374999999996</v>
+        <v>25.297058823529408</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13408,7 +13512,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.65816808816878591</v>
+        <v>0.64585191169819822</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13496,7 +13600,9 @@
       <c r="AB67" s="56">
         <v>23.7</v>
       </c>
-      <c r="AC67" s="56"/>
+      <c r="AC67" s="56">
+        <v>24.9</v>
+      </c>
       <c r="AD67" s="56"/>
       <c r="AE67" s="56"/>
       <c r="AF67" s="56"/>
@@ -13511,11 +13617,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.413888888888888</v>
+        <v>25.386842105263156</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13523,7 +13629,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.88880138614586812</v>
+        <v>0.86175460252013636</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13611,7 +13717,9 @@
       <c r="AB68" s="56">
         <v>24.625</v>
       </c>
-      <c r="AC68" s="56"/>
+      <c r="AC68" s="56">
+        <v>24.7</v>
+      </c>
       <c r="AD68" s="56"/>
       <c r="AE68" s="56"/>
       <c r="AF68" s="56"/>
@@ -13626,11 +13734,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.008333333333333</v>
+        <v>24.992105263157892</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13638,7 +13746,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.68593564670132423</v>
+        <v>0.66970757652588375</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13831,7 +13939,9 @@
       <c r="AB70" s="56">
         <v>26.13333333333334</v>
       </c>
-      <c r="AC70" s="56"/>
+      <c r="AC70" s="56">
+        <v>25.13333333333334</v>
+      </c>
       <c r="AD70" s="56"/>
       <c r="AE70" s="56"/>
       <c r="AF70" s="56"/>
@@ -13846,11 +13956,11 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>25.988888888888891</v>
+        <v>25.943859649122807</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13858,7 +13968,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.32644597523536234</v>
+        <v>0.28141673546927848</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13943,10 +14053,10 @@
       <c r="AA71" s="56">
         <v>25.666666666666671</v>
       </c>
-      <c r="AB71" s="56">
-        <v>23</v>
-      </c>
-      <c r="AC71" s="56"/>
+      <c r="AB71" s="99"/>
+      <c r="AC71" s="56">
+        <v>23.6</v>
+      </c>
       <c r="AD71" s="56"/>
       <c r="AE71" s="56"/>
       <c r="AF71" s="56"/>
@@ -13965,7 +14075,7 @@
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.300000000000004</v>
+        <v>25.333333333333339</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13973,7 +14083,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.32679125704046541</v>
+        <v>0.3601245903738004</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14160,9 +14270,15 @@
       <c r="Z73" s="56">
         <v>21.35</v>
       </c>
-      <c r="AA73" s="56"/>
-      <c r="AB73" s="56"/>
-      <c r="AC73" s="56"/>
+      <c r="AA73" s="56">
+        <v>21.45</v>
+      </c>
+      <c r="AB73" s="56">
+        <v>19.75</v>
+      </c>
+      <c r="AC73" s="56">
+        <v>19.95</v>
+      </c>
       <c r="AD73" s="56"/>
       <c r="AE73" s="56"/>
       <c r="AF73" s="56"/>
@@ -14177,11 +14293,11 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>20.368750000000002</v>
+        <v>20.371052631578948</v>
       </c>
       <c r="AR73" s="71">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14189,7 +14305,7 @@
       </c>
       <c r="AS73" s="71">
         <f t="shared" si="5"/>
-        <v>0.3702512506398925</v>
+        <v>0.37255388221883834</v>
       </c>
     </row>
     <row r="74" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14277,7 +14393,9 @@
       <c r="AB74" s="56">
         <v>15.4</v>
       </c>
-      <c r="AC74" s="56"/>
+      <c r="AC74" s="56">
+        <v>15.06666666666667</v>
+      </c>
       <c r="AD74" s="56"/>
       <c r="AE74" s="56"/>
       <c r="AF74" s="56"/>
@@ -14292,11 +14410,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>15.505555555555551</v>
+        <v>15.482456140350871</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14304,7 +14422,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.32451186358876072</v>
+        <v>0.30141244838408099</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14392,7 +14510,9 @@
       <c r="AB75" s="56">
         <v>20.2</v>
       </c>
-      <c r="AC75" s="56"/>
+      <c r="AC75" s="56">
+        <v>20.45</v>
+      </c>
       <c r="AD75" s="56"/>
       <c r="AE75" s="56"/>
       <c r="AF75" s="56"/>
@@ -14407,11 +14527,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>20.615277777777777</v>
+        <v>20.606578947368419</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14419,7 +14539,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.81531116625155775</v>
+        <v>0.80661233584219971</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14507,7 +14627,9 @@
       <c r="AB76" s="56">
         <v>21.4</v>
       </c>
-      <c r="AC76" s="56"/>
+      <c r="AC76" s="56">
+        <v>23.06666666666667</v>
+      </c>
       <c r="AD76" s="56"/>
       <c r="AE76" s="56"/>
       <c r="AF76" s="56"/>
@@ -14522,11 +14644,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>23.822222222222216</v>
+        <v>23.78245614035087</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14534,7 +14656,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>1.1389813662432964</v>
+        <v>1.0992152843719509</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14622,7 +14744,9 @@
       <c r="AB77" s="56">
         <v>28.85</v>
       </c>
-      <c r="AC77" s="56"/>
+      <c r="AC77" s="56">
+        <v>30.05</v>
+      </c>
       <c r="AD77" s="56"/>
       <c r="AE77" s="56"/>
       <c r="AF77" s="56"/>
@@ -14637,11 +14761,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>31.088888888888885</v>
+        <v>31.034210526315782</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14649,7 +14773,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.904959078366236</v>
+        <v>1.8502807157931329</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14731,7 +14855,9 @@
       <c r="AB78" s="56">
         <v>27.466666666666669</v>
       </c>
-      <c r="AC78" s="56"/>
+      <c r="AC78" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AD78" s="56"/>
       <c r="AE78" s="56"/>
       <c r="AF78" s="56"/>
@@ -14746,11 +14872,11 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.022222222222219</v>
+        <v>30.99583333333333</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14758,7 +14884,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>1.5531693377714895</v>
+        <v>1.5267804488826009</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14828,13 +14954,27 @@
       <c r="V79" s="56">
         <v>19.733333333333331</v>
       </c>
-      <c r="W79" s="56"/>
-      <c r="X79" s="56"/>
-      <c r="Y79" s="56"/>
-      <c r="Z79" s="56"/>
-      <c r="AA79" s="56"/>
-      <c r="AB79" s="56"/>
-      <c r="AC79" s="56"/>
+      <c r="W79" s="56">
+        <v>20.466666666666669</v>
+      </c>
+      <c r="X79" s="56">
+        <v>20.2</v>
+      </c>
+      <c r="Y79" s="56">
+        <v>22.933333333333341</v>
+      </c>
+      <c r="Z79" s="56">
+        <v>21.2</v>
+      </c>
+      <c r="AA79" s="56">
+        <v>21.8</v>
+      </c>
+      <c r="AB79" s="56">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AC79" s="56">
+        <v>19.06666666666667</v>
+      </c>
       <c r="AD79" s="56"/>
       <c r="AE79" s="56"/>
       <c r="AF79" s="56"/>
@@ -14849,19 +14989,19 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="AQ79" s="71" t="str">
+        <v>19</v>
+      </c>
+      <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20.564912280701751</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.306579428930519</v>
       </c>
-      <c r="AS79" s="71" t="str">
+      <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.2583328517712324</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14947,7 +15087,9 @@
       <c r="AB80" s="56">
         <v>23</v>
       </c>
-      <c r="AC80" s="56"/>
+      <c r="AC80" s="56">
+        <v>24.15</v>
+      </c>
       <c r="AD80" s="56"/>
       <c r="AE80" s="56"/>
       <c r="AF80" s="56"/>
@@ -14962,11 +15104,11 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v>23.858823529411762</v>
+        <v>23.874999999999996</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14974,7 +15116,7 @@
       </c>
       <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v>-0.31580637668000833</v>
+        <v>-0.29962990609177353</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15062,7 +15204,9 @@
       <c r="AB81" s="56">
         <v>28.066666666666659</v>
       </c>
-      <c r="AC81" s="56"/>
+      <c r="AC81" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="AD81" s="56"/>
       <c r="AE81" s="56"/>
       <c r="AF81" s="56"/>
@@ -15077,11 +15221,11 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>25.724074074074071</v>
+        <v>25.752631578947366</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15089,7 +15233,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>0.55035161665249177</v>
+        <v>0.57890912152578622</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15317,7 +15461,9 @@
       </c>
       <c r="AA84" s="56"/>
       <c r="AB84" s="56"/>
-      <c r="AC84" s="56"/>
+      <c r="AC84" s="56">
+        <v>30.55</v>
+      </c>
       <c r="AD84" s="56"/>
       <c r="AE84" s="56"/>
       <c r="AF84" s="56"/>
@@ -15332,7 +15478,7 @@
       <c r="AO84" s="56"/>
       <c r="AP84" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ84" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15432,7 +15578,9 @@
       <c r="AB85" s="56">
         <v>29.35</v>
       </c>
-      <c r="AC85" s="56"/>
+      <c r="AC85" s="56">
+        <v>29.95</v>
+      </c>
       <c r="AD85" s="56"/>
       <c r="AE85" s="56"/>
       <c r="AF85" s="56"/>
@@ -15447,11 +15595,11 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>29.763888888888882</v>
+        <v>29.773684210526312</v>
       </c>
       <c r="AR85" s="71">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15459,7 +15607,7 @@
       </c>
       <c r="AS85" s="71">
         <f t="shared" si="5"/>
-        <v>1.1518057273340929</v>
+        <v>1.1616010489715229</v>
       </c>
     </row>
     <row r="86" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15547,7 +15695,9 @@
       <c r="AB86" s="56">
         <v>29.75</v>
       </c>
-      <c r="AC86" s="56"/>
+      <c r="AC86" s="56">
+        <v>31.35</v>
+      </c>
       <c r="AD86" s="56"/>
       <c r="AE86" s="56"/>
       <c r="AF86" s="56"/>
@@ -15562,11 +15712,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>32.508333333333333</v>
+        <v>32.44736842105263</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15574,7 +15724,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>3.5021433608709422</v>
+        <v>3.4411784485902395</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15662,7 +15812,9 @@
       <c r="AB87" s="56">
         <v>30.65</v>
       </c>
-      <c r="AC87" s="56"/>
+      <c r="AC87" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AD87" s="56"/>
       <c r="AE87" s="56"/>
       <c r="AF87" s="56"/>
@@ -15677,11 +15829,11 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>30.494444444444451</v>
+        <v>30.410526315789479</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15689,7 +15841,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>1.8035698284690405</v>
+        <v>1.7196516998140687</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15999,7 +16151,9 @@
       <c r="AB90" s="56">
         <v>16.75</v>
       </c>
-      <c r="AC90" s="56"/>
+      <c r="AC90" s="56">
+        <v>15.93333333333333</v>
+      </c>
       <c r="AD90" s="56"/>
       <c r="AE90" s="56"/>
       <c r="AF90" s="56"/>
@@ -16014,11 +16168,11 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>17.894444444444446</v>
+        <v>17.791228070175439</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16026,7 +16180,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>1.7311003584229745</v>
+        <v>1.6278839841539678</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16114,7 +16268,9 @@
       <c r="AB91" s="56">
         <v>23.93333333333333</v>
       </c>
-      <c r="AC91" s="56"/>
+      <c r="AC91" s="56">
+        <v>22</v>
+      </c>
       <c r="AD91" s="56"/>
       <c r="AE91" s="56"/>
       <c r="AF91" s="56"/>
@@ -16129,11 +16285,11 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>23.86296296296296</v>
+        <v>23.764912280701754</v>
       </c>
       <c r="AR91" s="71">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16141,7 +16297,7 @@
       </c>
       <c r="AS91" s="71">
         <f t="shared" si="5"/>
-        <v>1.7534750970933395</v>
+        <v>1.6554244148321331</v>
       </c>
     </row>
     <row r="92" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16229,7 +16385,9 @@
       <c r="AB92" s="56">
         <v>17.25</v>
       </c>
-      <c r="AC92" s="56"/>
+      <c r="AC92" s="56">
+        <v>16.850000000000001</v>
+      </c>
       <c r="AD92" s="56"/>
       <c r="AE92" s="56"/>
       <c r="AF92" s="56"/>
@@ -16244,11 +16402,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.470833333333335</v>
+        <v>17.438157894736843</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16256,7 +16414,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.3756061873987662</v>
+        <v>1.3429307488022744</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16344,7 +16502,9 @@
       <c r="AB93" s="56">
         <v>16.25</v>
       </c>
-      <c r="AC93" s="56"/>
+      <c r="AC93" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AD93" s="56"/>
       <c r="AE93" s="56"/>
       <c r="AF93" s="56"/>
@@ -16359,11 +16519,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>14.636111111111111</v>
+        <v>14.63421052631579</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16371,7 +16531,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.0033029749592508</v>
+        <v>1.0014023901639302</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16617,7 +16777,9 @@
       <c r="AB96" s="56">
         <v>14.1</v>
       </c>
-      <c r="AC96" s="56"/>
+      <c r="AC96" s="56">
+        <v>13.9</v>
+      </c>
       <c r="AD96" s="56"/>
       <c r="AE96" s="56"/>
       <c r="AF96" s="56"/>
@@ -16632,11 +16794,11 @@
       <c r="AO96" s="56"/>
       <c r="AP96" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ96" s="71">
         <f t="shared" si="4"/>
-        <v>13.222222222222223</v>
+        <v>13.257894736842108</v>
       </c>
       <c r="AR96" s="71" t="str">
         <f>IFERROR(VLOOKUP(A96,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16728,7 +16890,9 @@
       <c r="AB97" s="56">
         <v>15.83333333333333</v>
       </c>
-      <c r="AC97" s="56"/>
+      <c r="AC97" s="56">
+        <v>13.633333333333329</v>
+      </c>
       <c r="AD97" s="56"/>
       <c r="AE97" s="56"/>
       <c r="AF97" s="56"/>
@@ -16743,11 +16907,11 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ97" s="71">
         <f t="shared" si="4"/>
-        <v>14.541666666666668</v>
+        <v>14.488235294117647</v>
       </c>
       <c r="AR97" s="71" t="str">
         <f>IFERROR(VLOOKUP(A97,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16940,7 +17104,9 @@
       <c r="AB99" s="56">
         <v>13.6</v>
       </c>
-      <c r="AC99" s="56"/>
+      <c r="AC99" s="56">
+        <v>13.85</v>
+      </c>
       <c r="AD99" s="56"/>
       <c r="AE99" s="56"/>
       <c r="AF99" s="56"/>
@@ -16955,7 +17121,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17046,8 +17212,12 @@
         <v>12.866666666666671</v>
       </c>
       <c r="AA100" s="56"/>
-      <c r="AB100" s="56"/>
-      <c r="AC100" s="56"/>
+      <c r="AB100" s="56">
+        <v>13.866666666666671</v>
+      </c>
+      <c r="AC100" s="56">
+        <v>13.53333333333333</v>
+      </c>
       <c r="AD100" s="56"/>
       <c r="AE100" s="56"/>
       <c r="AF100" s="56"/>
@@ -17062,19 +17232,19 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ100" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13.041666666666668</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>11.246995369385891</v>
       </c>
-      <c r="AS100" s="71" t="str">
+      <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.794671297280777</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17314,7 +17484,9 @@
       <c r="AB103" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="AC103" s="56"/>
+      <c r="AC103" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="AD103" s="56"/>
       <c r="AE103" s="56"/>
       <c r="AF103" s="56"/>
@@ -17329,11 +17501,11 @@
       <c r="AO103" s="56"/>
       <c r="AP103" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ103" s="71">
         <f t="shared" si="4"/>
-        <v>17.955555555555559</v>
+        <v>17.94166666666667</v>
       </c>
       <c r="AR103" s="71">
         <f>IFERROR(VLOOKUP(A103,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17341,7 +17513,7 @@
       </c>
       <c r="AS103" s="71">
         <f t="shared" si="5"/>
-        <v>0.91101804707928835</v>
+        <v>0.89712915819039907</v>
       </c>
     </row>
     <row r="104" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17490,7 +17662,9 @@
       <c r="AB105" s="56">
         <v>15.33333333333333</v>
       </c>
-      <c r="AC105" s="56"/>
+      <c r="AC105" s="56">
+        <v>13.866666666666671</v>
+      </c>
       <c r="AD105" s="56"/>
       <c r="AE105" s="56"/>
       <c r="AF105" s="56"/>
@@ -17505,7 +17679,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17605,7 +17779,9 @@
       <c r="AB106" s="56">
         <v>13.775</v>
       </c>
-      <c r="AC106" s="56"/>
+      <c r="AC106" s="56">
+        <v>14.75</v>
+      </c>
       <c r="AD106" s="56"/>
       <c r="AE106" s="56"/>
       <c r="AF106" s="56"/>
@@ -17620,11 +17796,11 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ106" s="71">
         <f t="shared" si="4"/>
-        <v>13.888888888888888</v>
+        <v>13.934210526315789</v>
       </c>
       <c r="AR106" s="71">
         <f>IFERROR(VLOOKUP(A106,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17632,7 +17808,7 @@
       </c>
       <c r="AS106" s="71">
         <f t="shared" si="5"/>
-        <v>-0.34014402584292291</v>
+        <v>-0.29482238841602104</v>
       </c>
     </row>
     <row r="107" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17720,7 +17896,9 @@
       <c r="AB107" s="56">
         <v>14.65</v>
       </c>
-      <c r="AC107" s="56"/>
+      <c r="AC107" s="56">
+        <v>14.75</v>
+      </c>
       <c r="AD107" s="56"/>
       <c r="AE107" s="56"/>
       <c r="AF107" s="56"/>
@@ -17735,11 +17913,11 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ107" s="71">
         <f t="shared" si="4"/>
-        <v>14.491666666666665</v>
+        <v>14.505263157894735</v>
       </c>
       <c r="AR107" s="71">
         <f>IFERROR(VLOOKUP(A107,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17747,7 +17925,7 @@
       </c>
       <c r="AS107" s="71">
         <f t="shared" si="5"/>
-        <v>0.77790357915887576</v>
+        <v>0.79150007038694525</v>
       </c>
     </row>
     <row r="108" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17835,7 +18013,9 @@
       <c r="AB108" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="AC108" s="56"/>
+      <c r="AC108" s="56">
+        <v>17</v>
+      </c>
       <c r="AD108" s="56"/>
       <c r="AE108" s="56"/>
       <c r="AF108" s="56"/>
@@ -17850,11 +18030,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>17.499999999999993</v>
+        <v>17.473684210526311</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17862,7 +18042,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>0.56503796153310404</v>
+        <v>0.53872217205942263</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17950,7 +18130,9 @@
       <c r="AB109" s="56">
         <v>15.866666666666671</v>
       </c>
-      <c r="AC109" s="56"/>
+      <c r="AC109" s="56">
+        <v>16.733333333333331</v>
+      </c>
       <c r="AD109" s="56"/>
       <c r="AE109" s="56"/>
       <c r="AF109" s="56"/>
@@ -17965,11 +18147,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>15.840740740740744</v>
+        <v>15.887719298245617</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17977,7 +18159,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.33837721716755453</v>
+        <v>0.3853557746724281</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18065,7 +18247,9 @@
       <c r="AB110" s="56">
         <v>18.2</v>
       </c>
-      <c r="AC110" s="56"/>
+      <c r="AC110" s="56">
+        <v>18.266666666666669</v>
+      </c>
       <c r="AD110" s="56"/>
       <c r="AE110" s="56"/>
       <c r="AF110" s="56"/>
@@ -18080,11 +18264,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.729629629629628</v>
+        <v>17.757894736842101</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18092,7 +18276,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>1.3499333685275481</v>
+        <v>1.378198475740021</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18178,7 +18362,9 @@
       <c r="AB111" s="56">
         <v>19.466666666666669</v>
       </c>
-      <c r="AC111" s="56"/>
+      <c r="AC111" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AD111" s="56"/>
       <c r="AE111" s="56"/>
       <c r="AF111" s="56"/>
@@ -18193,11 +18379,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>18.992156862745098</v>
+        <v>19.003703703703703</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18205,7 +18391,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.86776939518856722</v>
+        <v>0.87931623614717225</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18384,7 +18570,9 @@
       <c r="AB113" s="56">
         <v>25.7</v>
       </c>
-      <c r="AC113" s="56"/>
+      <c r="AC113" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AD113" s="56"/>
       <c r="AE113" s="56"/>
       <c r="AF113" s="56"/>
@@ -18399,11 +18587,11 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>26.322222222222223</v>
+        <v>26.30263157894737</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18411,7 +18599,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.47774224446920144</v>
+        <v>0.4581516011943485</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18499,7 +18687,9 @@
       <c r="AB114" s="56">
         <v>19.666666666666671</v>
       </c>
-      <c r="AC114" s="56"/>
+      <c r="AC114" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="AD114" s="56"/>
       <c r="AE114" s="56"/>
       <c r="AF114" s="56"/>
@@ -18514,11 +18704,11 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ114" s="71">
         <f t="shared" si="4"/>
-        <v>19.288888888888888</v>
+        <v>19.242105263157892</v>
       </c>
       <c r="AR114" s="71">
         <f>IFERROR(VLOOKUP(A114,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18526,7 +18716,7 @@
       </c>
       <c r="AS114" s="71">
         <f t="shared" si="5"/>
-        <v>0.89238372254806819</v>
+        <v>0.84560009681707271</v>
       </c>
     </row>
     <row r="115" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18614,7 +18804,9 @@
       <c r="AB115" s="56">
         <v>25.266666666666669</v>
       </c>
-      <c r="AC115" s="56"/>
+      <c r="AC115" s="56">
+        <v>25.533333333333331</v>
+      </c>
       <c r="AD115" s="56"/>
       <c r="AE115" s="56"/>
       <c r="AF115" s="56"/>
@@ -18629,11 +18821,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.374074074074077</v>
+        <v>26.329824561403512</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18641,7 +18833,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>1.0052344683393279</v>
+        <v>0.96098495566876352</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18729,7 +18921,9 @@
       <c r="AB116" s="56">
         <v>29.066666666666659</v>
       </c>
-      <c r="AC116" s="56"/>
+      <c r="AC116" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AD116" s="56"/>
       <c r="AE116" s="56"/>
       <c r="AF116" s="56"/>
@@ -18744,11 +18938,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>28.588888888888889</v>
+        <v>28.578947368421051</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18756,7 +18950,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>2.8356093189964291</v>
+        <v>2.8256677985285918</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18844,7 +19038,9 @@
       <c r="AB117" s="56">
         <v>23.533333333333331</v>
       </c>
-      <c r="AC117" s="56"/>
+      <c r="AC117" s="56">
+        <v>24.733333333333331</v>
+      </c>
       <c r="AD117" s="56"/>
       <c r="AE117" s="56"/>
       <c r="AF117" s="56"/>
@@ -18859,11 +19055,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>23.400000000000002</v>
+        <v>23.470175438596495</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18871,7 +19067,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>1.6715591397849927</v>
+        <v>1.7417345783814859</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19139,7 +19335,9 @@
       <c r="AB120" s="56">
         <v>12.2</v>
       </c>
-      <c r="AC120" s="56"/>
+      <c r="AC120" s="56">
+        <v>11.133333333333329</v>
+      </c>
       <c r="AD120" s="56"/>
       <c r="AE120" s="56"/>
       <c r="AF120" s="56"/>
@@ -19154,11 +19352,11 @@
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ120" s="71">
         <f t="shared" si="4"/>
-        <v>12.27222222222222</v>
+        <v>12.212280701754384</v>
       </c>
       <c r="AR120" s="71">
         <f>IFERROR(VLOOKUP(A120,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19166,7 +19364,7 @@
       </c>
       <c r="AS120" s="71">
         <f t="shared" si="5"/>
-        <v>1.9694652262519412</v>
+        <v>1.909523705784105</v>
       </c>
     </row>
     <row r="121" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19328,8 +19526,12 @@
       <c r="AA122" s="56">
         <v>17.8</v>
       </c>
-      <c r="AB122" s="56"/>
-      <c r="AC122" s="56"/>
+      <c r="AB122" s="56">
+        <v>15.66666666666667</v>
+      </c>
+      <c r="AC122" s="56">
+        <v>15.33333333333333</v>
+      </c>
       <c r="AD122" s="56"/>
       <c r="AE122" s="56"/>
       <c r="AF122" s="56"/>
@@ -19344,11 +19546,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>15.720833333333333</v>
+        <v>15.696296296296294</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19356,7 +19558,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>0.67177437378982319</v>
+        <v>0.64723733675278439</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19511,7 +19713,9 @@
         <v>12.66666666666667</v>
       </c>
       <c r="AB124" s="56"/>
-      <c r="AC124" s="56"/>
+      <c r="AC124" s="56">
+        <v>12.133333333333329</v>
+      </c>
       <c r="AD124" s="56"/>
       <c r="AE124" s="56"/>
       <c r="AF124" s="56"/>
@@ -19526,7 +19730,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19863,7 +20067,9 @@
       <c r="AB128" s="56">
         <v>16</v>
       </c>
-      <c r="AC128" s="56"/>
+      <c r="AC128" s="56">
+        <v>14.233333333333331</v>
+      </c>
       <c r="AD128" s="56"/>
       <c r="AE128" s="56"/>
       <c r="AF128" s="56"/>
@@ -19878,11 +20084,11 @@
       <c r="AO128" s="56"/>
       <c r="AP128" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ128" s="71">
         <f t="shared" si="4"/>
-        <v>15.988888888888889</v>
+        <v>15.896491228070177</v>
       </c>
       <c r="AR128" s="71">
         <f>IFERROR(VLOOKUP(A128,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19890,7 +20096,7 @@
       </c>
       <c r="AS128" s="71">
         <f t="shared" si="5"/>
-        <v>1.7356465144214397</v>
+        <v>1.6432488536027279</v>
       </c>
     </row>
     <row r="129" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19978,7 +20184,9 @@
       <c r="AB129" s="56">
         <v>18.55</v>
       </c>
-      <c r="AC129" s="56"/>
+      <c r="AC129" s="56">
+        <v>17.5</v>
+      </c>
       <c r="AD129" s="56"/>
       <c r="AE129" s="56"/>
       <c r="AF129" s="56"/>
@@ -19993,11 +20201,11 @@
       <c r="AO129" s="56"/>
       <c r="AP129" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ129" s="71">
         <f t="shared" si="4"/>
-        <v>18.433333333333334</v>
+        <v>18.38421052631579</v>
       </c>
       <c r="AR129" s="71">
         <f>IFERROR(VLOOKUP(A129,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20005,7 +20213,7 @@
       </c>
       <c r="AS129" s="71">
         <f t="shared" si="5"/>
-        <v>1.6404363344293849</v>
+        <v>1.5913135274118417</v>
       </c>
     </row>
     <row r="130" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20172,7 +20380,9 @@
       <c r="AB131" s="56">
         <v>13.93333333333333</v>
       </c>
-      <c r="AC131" s="56"/>
+      <c r="AC131" s="56">
+        <v>13.46666666666667</v>
+      </c>
       <c r="AD131" s="56"/>
       <c r="AE131" s="56"/>
       <c r="AF131" s="56"/>
@@ -20187,11 +20397,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>14.046296296296298</v>
+        <v>14.015789473684212</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20199,7 +20409,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.4109565216424578</v>
+        <v>1.3804496990303718</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20287,7 +20497,9 @@
       <c r="AB132" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="AC132" s="56"/>
+      <c r="AC132" s="56">
+        <v>17</v>
+      </c>
       <c r="AD132" s="56"/>
       <c r="AE132" s="56"/>
       <c r="AF132" s="56"/>
@@ -20302,11 +20514,11 @@
       <c r="AO132" s="56"/>
       <c r="AP132" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ132" s="71">
         <f t="shared" si="4"/>
-        <v>18.014814814814812</v>
+        <v>17.961403508771927</v>
       </c>
       <c r="AR132" s="71">
         <f>IFERROR(VLOOKUP(A132,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20314,7 +20526,7 @@
       </c>
       <c r="AS132" s="71">
         <f t="shared" si="5"/>
-        <v>2.432635972431143</v>
+        <v>2.3792246663882572</v>
       </c>
     </row>
     <row r="133" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20402,7 +20614,9 @@
       <c r="AB133" s="56">
         <v>19.55</v>
       </c>
-      <c r="AC133" s="56"/>
+      <c r="AC133" s="56">
+        <v>18.25</v>
+      </c>
       <c r="AD133" s="56"/>
       <c r="AE133" s="56"/>
       <c r="AF133" s="56"/>
@@ -20417,11 +20631,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>21.172222222222224</v>
+        <v>21.018421052631581</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20429,7 +20643,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>2.4903415848170951</v>
+        <v>2.3365404152264517</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20517,7 +20731,9 @@
       <c r="AB134" s="56">
         <v>11.6</v>
       </c>
-      <c r="AC134" s="56"/>
+      <c r="AC134" s="56">
+        <v>12</v>
+      </c>
       <c r="AD134" s="56"/>
       <c r="AE134" s="56"/>
       <c r="AF134" s="56"/>
@@ -20532,11 +20748,11 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>11.029629629629628</v>
+        <v>11.080701754385963</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20544,7 +20760,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>0.17197955547316823</v>
+        <v>0.22305168022950284</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20711,7 +20927,9 @@
       <c r="AB136" s="56">
         <v>22.6</v>
       </c>
-      <c r="AC136" s="56"/>
+      <c r="AC136" s="56">
+        <v>21.2</v>
+      </c>
       <c r="AD136" s="56"/>
       <c r="AE136" s="56"/>
       <c r="AF136" s="56"/>
@@ -20726,11 +20944,11 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v>22.344444444444449</v>
+        <v>22.284210526315793</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20738,7 +20956,7 @@
       </c>
       <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v>2.3342233470960494</v>
+        <v>2.2739894289673934</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20826,7 +21044,9 @@
       <c r="AB137" s="56">
         <v>13.824999999999999</v>
       </c>
-      <c r="AC137" s="56"/>
+      <c r="AC137" s="56">
+        <v>13.45</v>
+      </c>
       <c r="AD137" s="56"/>
       <c r="AE137" s="56"/>
       <c r="AF137" s="56"/>
@@ -20841,11 +21061,11 @@
       <c r="AO137" s="56"/>
       <c r="AP137" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ137" s="71">
         <f t="shared" si="7"/>
-        <v>14.095833333333335</v>
+        <v>14.061842105263159</v>
       </c>
       <c r="AR137" s="71">
         <f>IFERROR(VLOOKUP(A137,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20853,7 +21073,7 @@
       </c>
       <c r="AS137" s="71">
         <f t="shared" si="8"/>
-        <v>1.1916155604993257</v>
+        <v>1.1576243324291493</v>
       </c>
     </row>
     <row r="138" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20941,7 +21161,9 @@
       <c r="AB138" s="56">
         <v>15.7</v>
       </c>
-      <c r="AC138" s="56"/>
+      <c r="AC138" s="56">
+        <v>15.05</v>
+      </c>
       <c r="AD138" s="56"/>
       <c r="AE138" s="56"/>
       <c r="AF138" s="56"/>
@@ -20956,11 +21178,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>16.780555555555555</v>
+        <v>16.689473684210526</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20968,7 +21190,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>1.1862049837856343</v>
+        <v>1.0951231124406053</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21278,9 @@
       <c r="AB139" s="56">
         <v>13.2</v>
       </c>
-      <c r="AC139" s="56"/>
+      <c r="AC139" s="56">
+        <v>13.33333333333333</v>
+      </c>
       <c r="AD139" s="56"/>
       <c r="AE139" s="56"/>
       <c r="AF139" s="56"/>
@@ -21071,11 +21295,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>13.581481481481482</v>
+        <v>13.56842105263158</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21083,7 +21307,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.567452084643433</v>
+        <v>1.5543916557935304</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21166,8 +21390,12 @@
       <c r="AA140" s="56">
         <v>12.35</v>
       </c>
-      <c r="AB140" s="56"/>
-      <c r="AC140" s="56"/>
+      <c r="AB140" s="56">
+        <v>10.95</v>
+      </c>
+      <c r="AC140" s="56">
+        <v>12.35</v>
+      </c>
       <c r="AD140" s="56"/>
       <c r="AE140" s="56"/>
       <c r="AF140" s="56"/>
@@ -21182,11 +21410,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>11.675000000000001</v>
+        <v>11.672222222222222</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21194,7 +21422,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>1.1460140235181999</v>
+        <v>1.1432362457404217</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,7 +21510,9 @@
       <c r="AB141" s="56">
         <v>28</v>
       </c>
-      <c r="AC141" s="56"/>
+      <c r="AC141" s="56">
+        <v>25.86666666666666</v>
+      </c>
       <c r="AD141" s="56"/>
       <c r="AE141" s="56"/>
       <c r="AF141" s="56"/>
@@ -21297,11 +21527,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>27.933333333333334</v>
+        <v>27.82456140350877</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21309,7 +21539,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>2.0713932411674527</v>
+        <v>1.9626213113428896</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21394,8 +21624,12 @@
       <c r="AA142" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="AB142" s="56"/>
-      <c r="AC142" s="56"/>
+      <c r="AB142" s="56">
+        <v>14.93333333333333</v>
+      </c>
+      <c r="AC142" s="56">
+        <v>15.53333333333333</v>
+      </c>
       <c r="AD142" s="56"/>
       <c r="AE142" s="56"/>
       <c r="AF142" s="56"/>
@@ -21410,11 +21644,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>15.658823529411768</v>
+        <v>15.6140350877193</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21422,7 +21656,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>-5.4062224502521516E-2</v>
+        <v>-9.88506661949895E-2</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21510,7 +21744,9 @@
       <c r="AB143" s="56">
         <v>19.06666666666667</v>
       </c>
-      <c r="AC143" s="56"/>
+      <c r="AC143" s="56">
+        <v>20.466666666666669</v>
+      </c>
       <c r="AD143" s="56"/>
       <c r="AE143" s="56"/>
       <c r="AF143" s="56"/>
@@ -21525,11 +21761,11 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>19.359259259259257</v>
+        <v>19.417543859649118</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21537,7 +21773,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>0.31724272476113669</v>
+        <v>0.37552732515099763</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21738,7 +21974,9 @@
       <c r="AB145" s="56">
         <v>25.533333333333331</v>
       </c>
-      <c r="AC145" s="56"/>
+      <c r="AC145" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="AD145" s="56"/>
       <c r="AE145" s="56"/>
       <c r="AF145" s="56"/>
@@ -21753,11 +21991,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>25.148148148148152</v>
+        <v>25.207017543859653</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21765,7 +22003,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>1.6440906562847921</v>
+        <v>1.7029600519962926</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21849,7 +22087,9 @@
       <c r="AB146" s="56">
         <v>29.533333333333331</v>
       </c>
-      <c r="AC146" s="56"/>
+      <c r="AC146" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AD146" s="56"/>
       <c r="AE146" s="56"/>
       <c r="AF146" s="56"/>
@@ -21864,11 +22104,11 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>30.62083333333333</v>
+        <v>30.537254901960782</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21876,7 +22116,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.9793021024785489</v>
+        <v>1.8957236711060013</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21964,7 +22204,9 @@
       <c r="AB147" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="AC147" s="56"/>
+      <c r="AC147" s="56">
+        <v>23.266666666666669</v>
+      </c>
       <c r="AD147" s="56"/>
       <c r="AE147" s="56"/>
       <c r="AF147" s="56"/>
@@ -21979,11 +22221,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>23.8</v>
+        <v>23.771929824561404</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21991,7 +22233,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.9239322270471497</v>
+        <v>1.8958620516085531</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22429,7 +22671,9 @@
       <c r="AB152" s="56">
         <v>19.95</v>
       </c>
-      <c r="AC152" s="56"/>
+      <c r="AC152" s="56">
+        <v>19.05</v>
+      </c>
       <c r="AD152" s="56"/>
       <c r="AE152" s="56"/>
       <c r="AF152" s="56"/>
@@ -22444,11 +22688,11 @@
       <c r="AO152" s="56"/>
       <c r="AP152" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ152" s="71">
         <f t="shared" si="7"/>
-        <v>20.711111111111112</v>
+        <v>20.623684210526317</v>
       </c>
       <c r="AR152" s="71">
         <f>IFERROR(VLOOKUP(A152,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22456,7 +22700,7 @@
       </c>
       <c r="AS152" s="71">
         <f t="shared" si="8"/>
-        <v>1.1974903567161732</v>
+        <v>1.1100634561313782</v>
       </c>
     </row>
     <row r="153" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22544,7 +22788,9 @@
       <c r="AB153" s="56">
         <v>29.466666666666669</v>
       </c>
-      <c r="AC153" s="56"/>
+      <c r="AC153" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AD153" s="56"/>
       <c r="AE153" s="56"/>
       <c r="AF153" s="56"/>
@@ -22559,11 +22805,11 @@
       <c r="AO153" s="56"/>
       <c r="AP153" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ153" s="71">
         <f t="shared" si="7"/>
-        <v>29.159259259259258</v>
+        <v>29.140350877192979</v>
       </c>
       <c r="AR153" s="71">
         <f>IFERROR(VLOOKUP(A153,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22571,7 +22817,7 @@
       </c>
       <c r="AS153" s="71">
         <f t="shared" si="8"/>
-        <v>1.4364726984034597</v>
+        <v>1.4175643163371809</v>
       </c>
     </row>
     <row r="154" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22841,7 +23087,9 @@
       <c r="AB156" s="56">
         <v>30.86666666666666</v>
       </c>
-      <c r="AC156" s="56"/>
+      <c r="AC156" s="56">
+        <v>29.933333333333341</v>
+      </c>
       <c r="AD156" s="56"/>
       <c r="AE156" s="56"/>
       <c r="AF156" s="56"/>
@@ -22856,11 +23104,11 @@
       <c r="AO156" s="56"/>
       <c r="AP156" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ156" s="71">
         <f t="shared" si="7"/>
-        <v>30.43333333333333</v>
+        <v>30.403921568627453</v>
       </c>
       <c r="AR156" s="71">
         <f>IFERROR(VLOOKUP(A156,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22868,7 +23116,7 @@
       </c>
       <c r="AS156" s="71">
         <f t="shared" si="8"/>
-        <v>2.41492116625313</v>
+        <v>2.3855094015472531</v>
       </c>
     </row>
     <row r="157" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23067,7 +23315,9 @@
       <c r="AB158" s="56">
         <v>28.06666666666667</v>
       </c>
-      <c r="AC158" s="56"/>
+      <c r="AC158" s="56">
+        <v>26</v>
+      </c>
       <c r="AD158" s="56"/>
       <c r="AE158" s="56"/>
       <c r="AF158" s="56"/>
@@ -23082,11 +23332,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>27.296296296296301</v>
+        <v>27.228070175438603</v>
       </c>
       <c r="AR158" s="71" t="str">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23163,8 +23413,12 @@
       <c r="AA159" s="56">
         <v>19.266666666666669</v>
       </c>
-      <c r="AB159" s="56"/>
-      <c r="AC159" s="56"/>
+      <c r="AB159" s="56">
+        <v>19.266666666666669</v>
+      </c>
+      <c r="AC159" s="56">
+        <v>17.666666666666671</v>
+      </c>
       <c r="AD159" s="56"/>
       <c r="AE159" s="56"/>
       <c r="AF159" s="56"/>
@@ -23179,7 +23433,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23279,7 +23533,9 @@
       <c r="AB160" s="56">
         <v>29.06666666666667</v>
       </c>
-      <c r="AC160" s="56"/>
+      <c r="AC160" s="56">
+        <v>29.333333333333329</v>
+      </c>
       <c r="AD160" s="56"/>
       <c r="AE160" s="56"/>
       <c r="AF160" s="56"/>
@@ -23294,11 +23550,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>29.162962962962965</v>
+        <v>29.17192982456141</v>
       </c>
       <c r="AR160" s="71">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23306,7 +23562,7 @@
       </c>
       <c r="AS160" s="71">
         <f t="shared" si="8"/>
-        <v>0.58942557508868632</v>
+        <v>0.59839243668713138</v>
       </c>
     </row>
     <row r="161" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23394,7 +23650,9 @@
       <c r="AB161" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="AC161" s="56"/>
+      <c r="AC161" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AD161" s="56"/>
       <c r="AE161" s="56"/>
       <c r="AF161" s="56"/>
@@ -23409,11 +23667,11 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ161" s="71">
         <f t="shared" si="7"/>
-        <v>21.540740740740738</v>
+        <v>21.543859649122805</v>
       </c>
       <c r="AR161" s="71">
         <f>IFERROR(VLOOKUP(A161,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23421,7 +23679,7 @@
       </c>
       <c r="AS161" s="71">
         <f t="shared" si="8"/>
-        <v>0.29131692514015839</v>
+        <v>0.29443583352222547</v>
       </c>
     </row>
     <row r="162" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23509,7 +23767,9 @@
       <c r="AB162" s="56">
         <v>25.75</v>
       </c>
-      <c r="AC162" s="56"/>
+      <c r="AC162" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AD162" s="56"/>
       <c r="AE162" s="56"/>
       <c r="AF162" s="56"/>
@@ -23524,11 +23784,11 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>25.516666666666669</v>
+        <v>25.539473684210531</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23536,7 +23796,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>1.7187390575065891</v>
+        <v>1.7415460750504508</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23699,7 +23959,9 @@
       <c r="AB164" s="56">
         <v>15.133333333333329</v>
       </c>
-      <c r="AC164" s="56"/>
+      <c r="AC164" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="AD164" s="56"/>
       <c r="AE164" s="56"/>
       <c r="AF164" s="56"/>
@@ -23714,11 +23976,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>15.079166666666667</v>
+        <v>14.941176470588236</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23726,7 +23988,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.4806971326165268</v>
+        <v>1.3427069365380948</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23810,7 +24072,9 @@
       <c r="AB165" s="56">
         <v>20.666666666666671</v>
       </c>
-      <c r="AC165" s="56"/>
+      <c r="AC165" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="AD165" s="56"/>
       <c r="AE165" s="56"/>
       <c r="AF165" s="56"/>
@@ -23825,11 +24089,11 @@
       <c r="AO165" s="56"/>
       <c r="AP165" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ165" s="71">
         <f t="shared" si="7"/>
-        <v>20.808333333333337</v>
+        <v>20.784313725490197</v>
       </c>
       <c r="AR165" s="71">
         <f>IFERROR(VLOOKUP(A165,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23837,7 +24101,7 @@
       </c>
       <c r="AS165" s="71">
         <f t="shared" si="8"/>
-        <v>1.7727655237226969</v>
+        <v>1.7487459158795566</v>
       </c>
     </row>
     <row r="166" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23921,7 +24185,9 @@
       </c>
       <c r="AA166" s="56"/>
       <c r="AB166" s="56"/>
-      <c r="AC166" s="56"/>
+      <c r="AC166" s="56">
+        <v>25.75</v>
+      </c>
       <c r="AD166" s="56"/>
       <c r="AE166" s="56"/>
       <c r="AF166" s="56"/>
@@ -23936,11 +24202,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>28.334374999999998</v>
+        <v>28.182352941176468</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23948,7 +24214,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>2.2685105339334193</v>
+        <v>2.1164884751098896</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24036,7 +24302,9 @@
       <c r="AB167" s="56">
         <v>9.0500000000000007</v>
       </c>
-      <c r="AC167" s="56"/>
+      <c r="AC167" s="56">
+        <v>8.5500000000000007</v>
+      </c>
       <c r="AD167" s="56"/>
       <c r="AE167" s="56"/>
       <c r="AF167" s="56"/>
@@ -24051,11 +24319,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>8.85</v>
+        <v>8.8342105263157897</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24063,7 +24331,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>0.30787571864546237</v>
+        <v>0.29208624496125246</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24250,7 +24518,9 @@
       <c r="AB169" s="56">
         <v>20</v>
       </c>
-      <c r="AC169" s="56"/>
+      <c r="AC169" s="56">
+        <v>18.733333333333331</v>
+      </c>
       <c r="AD169" s="56"/>
       <c r="AE169" s="56"/>
       <c r="AF169" s="56"/>
@@ -24265,11 +24535,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>21.078431372549023</v>
+        <v>20.94814814814815</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24277,7 +24547,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>2.1495053502971047</v>
+        <v>2.0192221258962313</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24361,7 +24631,9 @@
       <c r="AB170" s="56">
         <v>24.8</v>
       </c>
-      <c r="AC170" s="56"/>
+      <c r="AC170" s="56">
+        <v>24.45</v>
+      </c>
       <c r="AD170" s="56"/>
       <c r="AE170" s="56"/>
       <c r="AF170" s="56"/>
@@ -24376,11 +24648,11 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>25.709375000000001</v>
+        <v>25.63529411764706</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24388,7 +24660,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>1.2707466314881231</v>
+        <v>1.1966657491351818</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24476,7 +24748,9 @@
       <c r="AB171" s="56">
         <v>25.35</v>
       </c>
-      <c r="AC171" s="56"/>
+      <c r="AC171" s="56">
+        <v>23.6</v>
+      </c>
       <c r="AD171" s="56"/>
       <c r="AE171" s="56"/>
       <c r="AF171" s="56"/>
@@ -24491,11 +24765,11 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>25.25324074074074</v>
+        <v>25.166228070175439</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24503,7 +24777,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.198832138590209</v>
+        <v>1.1118194680249083</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24589,7 +24863,9 @@
       <c r="AB172" s="56">
         <v>14.8</v>
       </c>
-      <c r="AC172" s="56"/>
+      <c r="AC172" s="56">
+        <v>13.6</v>
+      </c>
       <c r="AD172" s="56"/>
       <c r="AE172" s="56"/>
       <c r="AF172" s="56"/>
@@ -24604,11 +24880,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>13.90980392156863</v>
+        <v>13.892592592592594</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24616,7 +24892,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.8490520638967691</v>
+        <v>1.8318407349207337</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25060,7 +25336,9 @@
       <c r="AB177" s="56">
         <v>18.850000000000001</v>
       </c>
-      <c r="AC177" s="56"/>
+      <c r="AC177" s="56">
+        <v>16.95</v>
+      </c>
       <c r="AD177" s="56"/>
       <c r="AE177" s="56"/>
       <c r="AF177" s="56"/>
@@ -25075,19 +25353,19 @@
       <c r="AO177" s="56"/>
       <c r="AP177" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ177" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ177" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>18.899999999999999</v>
       </c>
       <c r="AR177" s="71">
         <f>IFERROR(VLOOKUP(A177,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>17.587583683516652</v>
       </c>
-      <c r="AS177" s="71" t="str">
+      <c r="AS177" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.3124163164833469</v>
       </c>
     </row>
     <row r="178" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25254,7 +25532,9 @@
       <c r="AB179" s="56">
         <v>29.4</v>
       </c>
-      <c r="AC179" s="56"/>
+      <c r="AC179" s="56">
+        <v>29.93333333333333</v>
+      </c>
       <c r="AD179" s="56"/>
       <c r="AE179" s="56"/>
       <c r="AF179" s="56"/>
@@ -25269,11 +25549,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>30.992592592592587</v>
+        <v>30.93684210526315</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25281,7 +25561,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>2.4593562050227753</v>
+        <v>2.4036057176933383</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25527,7 +25807,9 @@
       <c r="AB182" s="56">
         <v>27.2</v>
       </c>
-      <c r="AC182" s="56"/>
+      <c r="AC182" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="AD182" s="56"/>
       <c r="AE182" s="56"/>
       <c r="AF182" s="56"/>
@@ -25542,11 +25824,11 @@
       <c r="AO182" s="56"/>
       <c r="AP182" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ182" s="71">
         <f t="shared" si="7"/>
-        <v>27.970370370370372</v>
+        <v>27.926315789473687</v>
       </c>
       <c r="AR182" s="71">
         <f>IFERROR(VLOOKUP(A182,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25554,7 +25836,7 @@
       </c>
       <c r="AS182" s="71">
         <f t="shared" si="8"/>
-        <v>1.331999152753383</v>
+        <v>1.2879445718566984</v>
       </c>
     </row>
     <row r="183" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25634,7 +25916,9 @@
       <c r="AB183" s="56">
         <v>28.13333333333334</v>
       </c>
-      <c r="AC183" s="56"/>
+      <c r="AC183" s="56">
+        <v>28.93333333333333</v>
+      </c>
       <c r="AD183" s="56"/>
       <c r="AE183" s="56"/>
       <c r="AF183" s="56"/>
@@ -25649,19 +25933,19 @@
       <c r="AO183" s="56"/>
       <c r="AP183" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ183" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ183" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>28.711111111111112</v>
       </c>
       <c r="AR183" s="71">
         <f>IFERROR(VLOOKUP(A183,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.608632285011371</v>
       </c>
-      <c r="AS183" s="71" t="str">
+      <c r="AS183" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.1024788260997411</v>
       </c>
     </row>
     <row r="184" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25907,7 +26191,9 @@
       <c r="AB186" s="56">
         <v>17.600000000000001</v>
       </c>
-      <c r="AC186" s="56"/>
+      <c r="AC186" s="56">
+        <v>16.733333333333331</v>
+      </c>
       <c r="AD186" s="56"/>
       <c r="AE186" s="56"/>
       <c r="AF186" s="56"/>
@@ -25922,11 +26208,11 @@
       <c r="AO186" s="56"/>
       <c r="AP186" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ186" s="71">
         <f t="shared" si="7"/>
-        <v>17.592592592592595</v>
+        <v>17.547368421052635</v>
       </c>
       <c r="AR186" s="71">
         <f>IFERROR(VLOOKUP(A186,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25934,7 +26220,7 @@
       </c>
       <c r="AS186" s="71">
         <f t="shared" si="8"/>
-        <v>1.5970006030608648</v>
+        <v>1.5517764315209046</v>
       </c>
     </row>
     <row r="187" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26129,7 +26415,9 @@
       <c r="AB188" s="56">
         <v>31.6</v>
       </c>
-      <c r="AC188" s="56"/>
+      <c r="AC188" s="56">
+        <v>28.733333333333331</v>
+      </c>
       <c r="AD188" s="56"/>
       <c r="AE188" s="56"/>
       <c r="AF188" s="56"/>
@@ -26144,11 +26432,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>30.859259259259261</v>
+        <v>30.747368421052634</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26156,7 +26444,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.9427355977767924</v>
+        <v>1.8308447595701658</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26244,7 +26532,9 @@
       <c r="AB189" s="56">
         <v>19.399999999999999</v>
       </c>
-      <c r="AC189" s="56"/>
+      <c r="AC189" s="56">
+        <v>18.5</v>
+      </c>
       <c r="AD189" s="56"/>
       <c r="AE189" s="56"/>
       <c r="AF189" s="56"/>
@@ -26259,11 +26549,11 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>18.813888888888886</v>
+        <v>18.797368421052632</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26271,7 +26561,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>1.4266698742282777</v>
+        <v>1.4101494063920228</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26359,7 +26649,9 @@
       <c r="AB190" s="56">
         <v>26.333333333333329</v>
       </c>
-      <c r="AC190" s="56"/>
+      <c r="AC190" s="56">
+        <v>24.533333333333331</v>
+      </c>
       <c r="AD190" s="56"/>
       <c r="AE190" s="56"/>
       <c r="AF190" s="56"/>
@@ -26374,11 +26666,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>26.11851851851852</v>
+        <v>26.03508771929825</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26386,7 +26678,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>0.87401133770034889</v>
+        <v>0.79058053848007859</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26469,8 +26761,12 @@
       <c r="AA191" s="56">
         <v>27.95</v>
       </c>
-      <c r="AB191" s="56"/>
-      <c r="AC191" s="56"/>
+      <c r="AB191" s="56">
+        <v>25.55</v>
+      </c>
+      <c r="AC191" s="56">
+        <v>26.45</v>
+      </c>
       <c r="AD191" s="56"/>
       <c r="AE191" s="56"/>
       <c r="AF191" s="56"/>
@@ -26485,11 +26781,11 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>27.134374999999995</v>
+        <v>27.008333333333329</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26497,7 +26793,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>0.78160545999082487</v>
+        <v>0.65556379332415915</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26585,7 +26881,9 @@
       <c r="AB192" s="56">
         <v>20.6</v>
       </c>
-      <c r="AC192" s="56"/>
+      <c r="AC192" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AD192" s="56"/>
       <c r="AE192" s="56"/>
       <c r="AF192" s="56"/>
@@ -26600,11 +26898,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>21.237037037037041</v>
+        <v>21.228070175438599</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26612,7 +26910,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>-0.37062476002138922</v>
+        <v>-0.37959162161983073</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26700,7 +26998,9 @@
       <c r="AB193" s="56">
         <v>29.533333333333331</v>
       </c>
-      <c r="AC193" s="56"/>
+      <c r="AC193" s="56">
+        <v>27.666666666666671</v>
+      </c>
       <c r="AD193" s="56"/>
       <c r="AE193" s="56"/>
       <c r="AF193" s="56"/>
@@ -26715,11 +27015,11 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>28.211111111111109</v>
+        <v>28.182456140350872</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26727,7 +27027,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>2.5236229014013496</v>
+        <v>2.4949679306411134</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26815,7 +27115,9 @@
       <c r="AB194" s="56">
         <v>22.86666666666666</v>
       </c>
-      <c r="AC194" s="56"/>
+      <c r="AC194" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AD194" s="56"/>
       <c r="AE194" s="56"/>
       <c r="AF194" s="56"/>
@@ -26830,11 +27132,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>22.588888888888889</v>
+        <v>22.536842105263162</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26842,7 +27144,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>2.3651324173636183</v>
+        <v>2.3130856337378916</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26930,7 +27232,9 @@
       <c r="AB195" s="56">
         <v>25.266666666666669</v>
       </c>
-      <c r="AC195" s="56"/>
+      <c r="AC195" s="56">
+        <v>25.533333333333331</v>
+      </c>
       <c r="AD195" s="56"/>
       <c r="AE195" s="56"/>
       <c r="AF195" s="56"/>
@@ -26945,11 +27249,11 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>25.948148148148146</v>
+        <v>25.92631578947368</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26957,7 +27261,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.8207651469776174</v>
+        <v>1.7989327883031514</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27045,7 +27349,9 @@
       <c r="AB196" s="56">
         <v>21.95</v>
       </c>
-      <c r="AC196" s="56"/>
+      <c r="AC196" s="56">
+        <v>21</v>
+      </c>
       <c r="AD196" s="56"/>
       <c r="AE196" s="56"/>
       <c r="AF196" s="56"/>
@@ -27060,11 +27366,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>21.824999999999996</v>
+        <v>21.781578947368416</v>
       </c>
       <c r="AR196" s="71" t="str">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27160,7 +27466,9 @@
       <c r="AB197" s="56">
         <v>15.66666666666667</v>
       </c>
-      <c r="AC197" s="56"/>
+      <c r="AC197" s="56">
+        <v>16.466666666666669</v>
+      </c>
       <c r="AD197" s="56"/>
       <c r="AE197" s="56"/>
       <c r="AF197" s="56"/>
@@ -27174,20 +27482,20 @@
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
-        <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>18</v>
+        <f t="shared" ref="AP197:AP210" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
+        <v>19</v>
       </c>
       <c r="AQ197" s="71">
-        <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>16.666666666666671</v>
+        <f t="shared" ref="AQ197:AQ210" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
+        <v>16.656140350877195</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.78766040619119</v>
       </c>
       <c r="AS197" s="71">
-        <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>0.87900626047548158</v>
+        <f t="shared" ref="AS197:AS210" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
+        <v>0.86847994468600476</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27275,7 +27583,9 @@
       <c r="AB198" s="56">
         <v>15.1</v>
       </c>
-      <c r="AC198" s="56"/>
+      <c r="AC198" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AD198" s="56"/>
       <c r="AE198" s="56"/>
       <c r="AF198" s="56"/>
@@ -27290,11 +27600,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>14.766666666666671</v>
+        <v>14.757894736842109</v>
       </c>
       <c r="AR198" s="71">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27302,7 +27612,7 @@
       </c>
       <c r="AS198" s="71">
         <f t="shared" si="11"/>
-        <v>1.4010541988830312</v>
+        <v>1.3922822690584695</v>
       </c>
     </row>
     <row r="199" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27390,7 +27700,9 @@
       <c r="AB199" s="56">
         <v>24.9</v>
       </c>
-      <c r="AC199" s="56"/>
+      <c r="AC199" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AD199" s="56"/>
       <c r="AE199" s="56"/>
       <c r="AF199" s="56"/>
@@ -27405,11 +27717,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>27.261111111111106</v>
+        <v>27.202631578947365</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27417,7 +27729,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>1.7235818427802556</v>
+        <v>1.6651023106165148</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27503,7 +27815,9 @@
       <c r="AB200" s="56">
         <v>13.3</v>
       </c>
-      <c r="AC200" s="56"/>
+      <c r="AC200" s="56">
+        <v>13.2</v>
+      </c>
       <c r="AD200" s="56"/>
       <c r="AE200" s="56"/>
       <c r="AF200" s="56"/>
@@ -27518,11 +27832,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>13.420588235294119</v>
+        <v>13.408333333333333</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27530,7 +27844,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>0.61702427679019856</v>
+        <v>0.60476937482941295</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27611,8 +27925,12 @@
       <c r="AA201" s="56">
         <v>14.6</v>
       </c>
-      <c r="AB201" s="56"/>
-      <c r="AC201" s="56"/>
+      <c r="AB201" s="56">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="AC201" s="56">
+        <v>14.46666666666667</v>
+      </c>
       <c r="AD201" s="56"/>
       <c r="AE201" s="56"/>
       <c r="AF201" s="56"/>
@@ -27627,11 +27945,11 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>14.017777777777777</v>
+        <v>14.023529411764704</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27639,7 +27957,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>2.0469029272967365</v>
+        <v>2.0526545612836635</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27828,7 +28146,9 @@
       <c r="AB203" s="56">
         <v>15.2</v>
       </c>
-      <c r="AC203" s="56"/>
+      <c r="AC203" s="56">
+        <v>13.45</v>
+      </c>
       <c r="AD203" s="56"/>
       <c r="AE203" s="56"/>
       <c r="AF203" s="56"/>
@@ -27843,11 +28163,11 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ203" s="71">
         <f t="shared" si="10"/>
-        <v>14.394444444444442</v>
+        <v>14.344736842105261</v>
       </c>
       <c r="AR203" s="71">
         <f>IFERROR(VLOOKUP(A203,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27855,7 +28175,7 @@
       </c>
       <c r="AS203" s="71">
         <f t="shared" si="11"/>
-        <v>0.97955032762677163</v>
+        <v>0.92984272528759071</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28149,7 +28469,9 @@
       <c r="AB206" s="56">
         <v>14.5</v>
       </c>
-      <c r="AC206" s="56"/>
+      <c r="AC206" s="56">
+        <v>14.85</v>
+      </c>
       <c r="AD206" s="56"/>
       <c r="AE206" s="56"/>
       <c r="AF206" s="56"/>
@@ -28164,11 +28486,11 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ206" s="71">
         <f t="shared" si="10"/>
-        <v>14.405882352941175</v>
+        <v>14.430555555555555</v>
       </c>
       <c r="AR206" s="71" t="str">
         <f>IFERROR(VLOOKUP(A206,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28264,7 +28586,9 @@
       <c r="AB207" s="56">
         <v>11.65</v>
       </c>
-      <c r="AC207" s="56"/>
+      <c r="AC207" s="56">
+        <v>11.2</v>
+      </c>
       <c r="AD207" s="56"/>
       <c r="AE207" s="56"/>
       <c r="AF207" s="56"/>
@@ -28279,11 +28603,11 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>11.06388888888889</v>
+        <v>11.071052631578949</v>
       </c>
       <c r="AR207" s="71" t="str">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28367,9 +28691,15 @@
       <c r="X208" s="56">
         <v>14.6</v>
       </c>
-      <c r="Y208" s="56"/>
-      <c r="Z208" s="56"/>
-      <c r="AA208" s="56"/>
+      <c r="Y208" s="56">
+        <v>15.75</v>
+      </c>
+      <c r="Z208" s="56">
+        <v>15.4</v>
+      </c>
+      <c r="AA208" s="56">
+        <v>16.899999999999999</v>
+      </c>
       <c r="AB208" s="56"/>
       <c r="AC208" s="56"/>
       <c r="AD208" s="56"/>
@@ -28386,19 +28716,19 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ208" s="71" t="str">
+        <v>17</v>
+      </c>
+      <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>15.741176470588236</v>
       </c>
       <c r="AR208" s="71">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>14.32967020528393</v>
       </c>
-      <c r="AS208" s="71" t="str">
+      <c r="AS208" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1.4115062653043058</v>
       </c>
     </row>
     <row r="209" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28601,7 +28931,9 @@
       <c r="AB210" s="56">
         <v>26.15</v>
       </c>
-      <c r="AC210" s="56"/>
+      <c r="AC210" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AD210" s="56"/>
       <c r="AE210" s="56"/>
       <c r="AF210" s="56"/>
@@ -28616,11 +28948,11 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v>25.255555555555546</v>
+        <v>25.310526315789467</v>
       </c>
       <c r="AR210" s="71" t="str">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
